--- a/SAKHALIN_ZAPROS/05_ООО_Челябинский_завод_трубопроводной_арм.xlsx
+++ b/SAKHALIN_ZAPROS/05_ООО_Челябинский_завод_трубопроводной_арм.xlsx
@@ -106,15 +106,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -692,7 +692,7 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -701,245 +701,265 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Запорная арматура ПТ11096-500М-02 (30с946нж) Dn 500 Pn 6. Под электропривод ПЭМ-В-1000-50-Е2М00-2-11 IP67 У1  с КИМ2-380/16-М00 производства АБС ЗЭиМ Автоматика г. Чебоксары.</t>
+          <t>Клапан обратный 19ч16бр Ду 250 Ру 16</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="9">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Клапан обратный поворотный чугунный 19ч16бр Ду250 Ру16</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="10">
         <f>M6*E6</f>
         <v/>
       </c>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Задвижка из нержавеющей стали  30нж41нж DN 150 PN 16 1исп.</t>
+          <t>Вентиль стальной фланцевый 15с65нж Ду25 Ру16</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="9">
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="9" t="n"/>
+      <c r="N7" s="10">
         <f>M7*E7</f>
         <v/>
       </c>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Вентиль запорный сальниковый DN050, PN16, корпус - чугун, фланцевый, штурвал</t>
+          <t>Клапан обратный приемный с сеткой фланцевый 16ч42р Ду80</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="9">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Клапан обратный приёмный с сеткой 16ч42р Ду80</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="10">
         <f>M8*E8</f>
         <v/>
       </c>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду15 Ру16</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Задвижка ДУ 100 РУ16 30НЖ41НЖ</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="9">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду15 Ру16</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="9" t="n"/>
+      <c r="N9" s="10">
         <f>M9*E9</f>
         <v/>
       </c>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
-      <c r="Q9" s="7" t="n"/>
+      <c r="O9" s="8" t="n"/>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Задвижка ДУ 100 РУ16 30НЖ41НЖ</t>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду20 Ру16</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="9">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду20 Ру16</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="10">
         <f>M10*E10</f>
         <v/>
       </c>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>№ 2</t>
+          <t>№ 1</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Задвижка ДУ 80 РУ16 30НЖ41НЖ</t>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду25 Ру16</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="9">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду25 Ру16</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="10">
         <f>M11*E11</f>
         <v/>
       </c>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="7" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -953,11 +973,11 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Клапан обратный 19ч16бр Ду 250 Ру 16</t>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду32 Ру16</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
@@ -968,24 +988,24 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Клапан обратный поворотный чугунный 19ч16бр Ду250 Ру16</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="9">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду32 Ру16</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="9" t="n"/>
+      <c r="N12" s="10">
         <f>M12*E12</f>
         <v/>
       </c>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="7" t="n"/>
+      <c r="O12" s="8" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="8" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -999,35 +1019,39 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Вентиль стальной фланцевый 15с65нж Ду25 Ру16</t>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду40 Ру16</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="8" t="n"/>
-      <c r="N13" s="9">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду40 Ру16</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="10">
         <f>M13*E13</f>
         <v/>
       </c>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
-      <c r="Q13" s="7" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1041,39 +1065,39 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Клапан обратный приемный с сеткой фланцевый 16ч42р Ду80</t>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду50 Ру16</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Клапан обратный приёмный с сеткой 16ч42р Ду80</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="9">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Вентиль чугунный муфтовый 15кч18п Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="10">
         <f>M14*E14</f>
         <v/>
       </c>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1087,39 +1111,35 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду15 Ру16</t>
+          <t>Задвижка чугунная с КОФ 30ч6бр Ду 400 Ру 10 1исп.</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду15 Ру16</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="9">
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="9" t="n"/>
+      <c r="N15" s="10">
         <f>M15*E15</f>
         <v/>
       </c>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="7" t="n"/>
+      <c r="O15" s="8" t="n"/>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1133,333 +1153,61 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду20 Ру16</t>
+          <t>Клапан запорный мембранный футерованный полиэтиленом фланцевый ручной 15ч75п1м Ду 25 Ру 10 кгс/смІ У3, корпус чугун, класс герметичности «С»    ГОСТ 9544-2015</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду20 Ру16</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="9">
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="10">
         <f>M16*E16</f>
         <v/>
       </c>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
     </row>
     <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду25 Ру16</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду25 Ру16</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="9">
-        <f>M17*E17</f>
+      <c r="A17" s="11" t="inlineStr"/>
+      <c r="B17" s="11" t="inlineStr"/>
+      <c r="C17" s="11" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr"/>
+      <c r="K17" s="11" t="inlineStr"/>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="N17" s="12">
+        <f>SUM(N6:N16)</f>
         <v/>
       </c>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="9">
-        <f>M18*E18</f>
-        <v/>
-      </c>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="7" t="n"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду40 Ру16</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду40 Ру16</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="9">
-        <f>M19*E19</f>
-        <v/>
-      </c>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду50 Ру16</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Вентиль чугунный муфтовый 15кч18п Ду50 Ру16</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="9">
-        <f>M20*E20</f>
-        <v/>
-      </c>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Задвижка чугунная с КОФ 30ч6бр Ду 400 Ру 10 1исп.</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="9">
-        <f>M21*E21</f>
-        <v/>
-      </c>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="7" t="n"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>№ 1</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Клапан запорный мембранный футерованный полиэтиленом фланцевый ручной 15ч75п1м Ду 25 Ру 10 кгс/смІ У3, корпус чугун, класс герметичности «С»    ГОСТ 9544-2015</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="9">
-        <f>M22*E22</f>
-        <v/>
-      </c>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
-      <c r="Q22" s="7" t="n"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="11" t="inlineStr"/>
-      <c r="B23" s="11" t="inlineStr"/>
-      <c r="C23" s="11" t="inlineStr"/>
-      <c r="D23" s="11" t="inlineStr"/>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="N23" s="12">
-        <f>SUM(N6:N22)</f>
-        <v/>
-      </c>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
-      <c r="Q23" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
